--- a/PyPiano/WA.xlsx
+++ b/PyPiano/WA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maste\Documents\PyProjects\PyPiano\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05F2AC3-585A-4D15-AA4A-B5C1888F5854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F23B7F9-9E69-4870-A070-79D4687964B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11918" yWindow="0" windowWidth="12165" windowHeight="14362" xr2:uid="{6F045668-9CAC-43E7-9718-A57DA70D28DA}"/>
+    <workbookView xWindow="2850" yWindow="4560" windowWidth="18000" windowHeight="10432" xr2:uid="{6F045668-9CAC-43E7-9718-A57DA70D28DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5997,7 +5997,7 @@
         <v>50</v>
       </c>
       <c r="D237">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E237">
         <v>164</v>

--- a/PyPiano/WA.xlsx
+++ b/PyPiano/WA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maste\Documents\PyProjects\PyPiano\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F23B7F9-9E69-4870-A070-79D4687964B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1787607E-B475-485C-BA93-2B63378CBB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2850" yWindow="4560" windowWidth="18000" windowHeight="10432" xr2:uid="{6F045668-9CAC-43E7-9718-A57DA70D28DA}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="17999" windowHeight="10432" xr2:uid="{6F045668-9CAC-43E7-9718-A57DA70D28DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="42">
   <si>
     <t>E</t>
   </si>
@@ -223,8 +223,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B7AA3B72-4838-436F-A7A6-21FDD27999CB}" name="Table1" displayName="Table1" ref="A1:G342" totalsRowShown="0">
-  <autoFilter ref="A1:G342" xr:uid="{B7AA3B72-4838-436F-A7A6-21FDD27999CB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B7AA3B72-4838-436F-A7A6-21FDD27999CB}" name="Table1" displayName="Table1" ref="A1:G344" totalsRowShown="0">
+  <autoFilter ref="A1:G344" xr:uid="{B7AA3B72-4838-436F-A7A6-21FDD27999CB}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C77D956E-E18B-4E3A-A696-58589DEBA14F}" name="Note"/>
     <tableColumn id="2" xr3:uid="{3118604E-D26F-49C2-87F5-AA552D67F67F}" name="Time"/>
@@ -555,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CA2910B-C0FF-435B-BF71-C7E7EE0CE8D0}">
-  <dimension ref="A1:G342"/>
+  <dimension ref="A1:G344"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -5968,7 +5968,7 @@
         <v>17</v>
       </c>
       <c r="B236" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C236">
         <v>49</v>
@@ -5988,16 +5988,16 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B237" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C237">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E237">
         <v>164</v>
@@ -6011,16 +6011,16 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B238" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C238">
         <v>50</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E238">
         <v>164</v>
@@ -6080,7 +6080,7 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B241" t="s">
         <v>0</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B242" t="s">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B243" t="s">
         <v>0</v>
@@ -6152,10 +6152,10 @@
         <v>20</v>
       </c>
       <c r="B244" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C244">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D244">
         <v>1</v>
@@ -6172,16 +6172,16 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B245" t="s">
         <v>0</v>
       </c>
       <c r="C245">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E245">
         <v>164</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B246" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C246">
         <v>51</v>
@@ -6218,7 +6218,7 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="B247" t="s">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>51</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E247">
         <v>164</v>
@@ -6241,7 +6241,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B248" t="s">
         <v>0</v>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B249" t="s">
         <v>0</v>
@@ -6287,7 +6287,7 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B250" t="s">
         <v>0</v>
@@ -6310,13 +6310,13 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B251" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C251">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D251">
         <v>1</v>
@@ -6333,13 +6333,13 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B252" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C252">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D252">
         <v>1</v>
@@ -6356,16 +6356,16 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B253" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C253">
         <v>52</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E253">
         <v>164</v>
@@ -6379,10 +6379,10 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B254" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C254">
         <v>52</v>
@@ -6402,16 +6402,16 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B255" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C255">
         <v>52</v>
       </c>
       <c r="D255">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E255">
         <v>164</v>
@@ -6451,13 +6451,13 @@
         <v>25</v>
       </c>
       <c r="B257" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C257">
         <v>52</v>
       </c>
       <c r="D257">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E257">
         <v>164</v>
@@ -6471,13 +6471,13 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B258" t="s">
         <v>0</v>
       </c>
       <c r="C258">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D258">
         <v>1</v>
@@ -6494,13 +6494,13 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B259" t="s">
         <v>0</v>
       </c>
       <c r="C259">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D259">
         <v>1</v>
@@ -6517,16 +6517,16 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B260" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C260">
         <v>53</v>
       </c>
       <c r="D260">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E260">
         <v>164</v>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B261" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C261">
         <v>53</v>
@@ -6563,16 +6563,16 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B262" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C262">
         <v>53</v>
       </c>
       <c r="D262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E262">
         <v>164</v>
@@ -6586,10 +6586,10 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B263" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C263">
         <v>53</v>
@@ -6609,16 +6609,16 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B264" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C264">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D264">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E264">
         <v>164</v>
@@ -6632,13 +6632,13 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B265" t="s">
         <v>0</v>
       </c>
       <c r="C265">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D265">
         <v>1</v>
@@ -6658,13 +6658,13 @@
         <v>38</v>
       </c>
       <c r="B266" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C266">
         <v>54</v>
       </c>
       <c r="D266">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E266">
         <v>164</v>
@@ -6678,13 +6678,13 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B267" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C267">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D267">
         <v>1</v>
@@ -6701,13 +6701,13 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B268" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C268">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -6724,16 +6724,16 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="B269" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C269">
         <v>55</v>
       </c>
       <c r="D269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E269">
         <v>164</v>
@@ -6747,10 +6747,10 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C270">
         <v>55</v>
@@ -6770,16 +6770,16 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="B271" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C271">
         <v>55</v>
       </c>
       <c r="D271">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E271">
         <v>164</v>
@@ -6793,10 +6793,10 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B272" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C272">
         <v>55</v>
@@ -6816,16 +6816,16 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B273" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C273">
         <v>55</v>
       </c>
       <c r="D273">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E273">
         <v>164</v>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B274" t="s">
         <v>24</v>
@@ -6862,7 +6862,7 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B275" t="s">
         <v>24</v>
@@ -6885,16 +6885,16 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B276" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C276">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E276">
         <v>164</v>
@@ -6908,13 +6908,13 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B277" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C277">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D277">
         <v>1</v>
@@ -6931,16 +6931,16 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B278" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C278">
         <v>56</v>
       </c>
       <c r="D278">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E278">
         <v>164</v>
@@ -6954,7 +6954,7 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B279" t="s">
         <v>0</v>
@@ -6977,10 +6977,10 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B280" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C280">
         <v>56</v>
@@ -7046,13 +7046,13 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B283" t="s">
         <v>0</v>
       </c>
       <c r="C283">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D283">
         <v>1</v>
@@ -7069,13 +7069,13 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B284" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C284">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D284">
         <v>1</v>
@@ -7092,10 +7092,10 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B285" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C285">
         <v>57</v>
@@ -7118,7 +7118,7 @@
         <v>26</v>
       </c>
       <c r="B286" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C286">
         <v>57</v>
@@ -7138,10 +7138,10 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B287" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C287">
         <v>57</v>
@@ -7161,16 +7161,16 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B288" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C288">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D288">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E288">
         <v>164</v>
@@ -7187,10 +7187,10 @@
         <v>38</v>
       </c>
       <c r="B289" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C289">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D289">
         <v>1</v>
@@ -7207,7 +7207,7 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B290" t="s">
         <v>3</v>
@@ -7216,7 +7216,7 @@
         <v>58</v>
       </c>
       <c r="D290">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E290">
         <v>164</v>
@@ -7230,7 +7230,7 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B291" t="s">
         <v>3</v>
@@ -7253,13 +7253,13 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B292" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C292">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D292">
         <v>1</v>
@@ -7276,13 +7276,13 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B293" t="s">
         <v>3</v>
       </c>
       <c r="C293">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D293">
         <v>1</v>
@@ -7299,7 +7299,7 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B294" t="s">
         <v>0</v>
@@ -7308,7 +7308,7 @@
         <v>59</v>
       </c>
       <c r="D294">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E294">
         <v>164</v>
@@ -7345,7 +7345,7 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B296" t="s">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>59</v>
       </c>
       <c r="D296">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E296">
         <v>164</v>
@@ -7368,10 +7368,10 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B297" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C297">
         <v>59</v>
@@ -7391,13 +7391,13 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B298" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C298">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D298">
         <v>1</v>
@@ -7414,13 +7414,13 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B299" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C299">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D299">
         <v>1</v>
@@ -7437,16 +7437,16 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B300" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C300">
         <v>60</v>
       </c>
       <c r="D300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E300">
         <v>164</v>
@@ -7460,10 +7460,10 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B301" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C301">
         <v>60</v>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B302" t="s">
         <v>0</v>
@@ -7492,7 +7492,7 @@
         <v>60</v>
       </c>
       <c r="D302">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E302">
         <v>164</v>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B303" t="s">
         <v>0</v>
@@ -7529,10 +7529,10 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B304" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C304">
         <v>60</v>
@@ -7552,13 +7552,13 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B305" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C305">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D305">
         <v>1</v>
@@ -7575,13 +7575,13 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B306" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C306">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D306">
         <v>1</v>
@@ -7598,16 +7598,16 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B307" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C307">
         <v>61</v>
       </c>
       <c r="D307">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E307">
         <v>164</v>
@@ -7621,7 +7621,7 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B308" t="s">
         <v>0</v>
@@ -7644,16 +7644,16 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B309" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C309">
         <v>61</v>
       </c>
       <c r="D309">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E309">
         <v>164</v>
@@ -7667,16 +7667,16 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B310" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C310">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D310">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E310">
         <v>164</v>
@@ -7696,10 +7696,10 @@
         <v>0</v>
       </c>
       <c r="C311">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D311">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E311">
         <v>164</v>
@@ -7713,16 +7713,16 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B312" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C312">
         <v>62</v>
       </c>
       <c r="D312">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E312">
         <v>164</v>
@@ -7736,7 +7736,7 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B313" t="s">
         <v>0</v>
@@ -7745,7 +7745,7 @@
         <v>62</v>
       </c>
       <c r="D313">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E313">
         <v>164</v>
@@ -7762,10 +7762,10 @@
         <v>31</v>
       </c>
       <c r="B314" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C314">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D314">
         <v>1</v>
@@ -7788,7 +7788,7 @@
         <v>0</v>
       </c>
       <c r="C315">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D315">
         <v>1</v>
@@ -7805,10 +7805,10 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B316" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C316">
         <v>63</v>
@@ -7828,7 +7828,7 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B317" t="s">
         <v>0</v>
@@ -7851,7 +7851,7 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B318" t="s">
         <v>3</v>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B319" t="s">
         <v>0</v>
@@ -7897,16 +7897,16 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B320" t="s">
         <v>3</v>
       </c>
       <c r="C320">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D320">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E320">
         <v>164</v>
@@ -7920,13 +7920,13 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B321" t="s">
         <v>0</v>
       </c>
       <c r="C321">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D321">
         <v>1</v>
@@ -7943,16 +7943,16 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B322" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C322">
         <v>64</v>
       </c>
       <c r="D322">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E322">
         <v>164</v>
@@ -7966,7 +7966,7 @@
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B323" t="s">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>64</v>
       </c>
       <c r="D323">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E323">
         <v>164</v>
@@ -7989,7 +7989,7 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B324" t="s">
         <v>0</v>
@@ -8012,16 +8012,16 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="B325" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C325">
         <v>64</v>
       </c>
       <c r="D325">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E325">
         <v>164</v>
@@ -8035,13 +8035,13 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B326" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C326">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D326">
         <v>1</v>
@@ -8058,16 +8058,16 @@
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B327" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C327">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D327">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E327">
         <v>164</v>
@@ -8081,16 +8081,16 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B328" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C328">
         <v>65</v>
       </c>
       <c r="D328">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E328">
         <v>164</v>
@@ -8104,10 +8104,10 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B329" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C329">
         <v>65</v>
@@ -8127,16 +8127,16 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B330" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C330">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D330">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E330">
         <v>164</v>
@@ -8150,13 +8150,13 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B331" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C331">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D331">
         <v>1</v>
@@ -8173,16 +8173,16 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B332" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C332">
         <v>66</v>
       </c>
       <c r="D332">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E332">
         <v>164</v>
@@ -8196,7 +8196,7 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B333" t="s">
         <v>0</v>
@@ -8222,13 +8222,13 @@
         <v>20</v>
       </c>
       <c r="B334" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C334">
         <v>66</v>
       </c>
       <c r="D334">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E334">
         <v>164</v>
@@ -8242,13 +8242,13 @@
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B335" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C335">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D335">
         <v>1</v>
@@ -8265,13 +8265,13 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B336" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C336">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D336">
         <v>1</v>
@@ -8288,16 +8288,16 @@
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B337" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C337">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D337">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E337">
         <v>164</v>
@@ -8311,7 +8311,7 @@
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B338" t="s">
         <v>3</v>
@@ -8320,7 +8320,7 @@
         <v>68</v>
       </c>
       <c r="D338">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E338">
         <v>164</v>
@@ -8334,7 +8334,7 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B339" t="s">
         <v>3</v>
@@ -8343,7 +8343,7 @@
         <v>68</v>
       </c>
       <c r="D339">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E339">
         <v>164</v>
@@ -8357,16 +8357,16 @@
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B340" t="s">
         <v>3</v>
       </c>
       <c r="C340">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D340">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E340">
         <v>164</v>
@@ -8380,16 +8380,16 @@
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B341" t="s">
         <v>3</v>
       </c>
       <c r="C341">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D341">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E341">
         <v>164</v>
@@ -8403,16 +8403,16 @@
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B342" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C342">
         <v>69</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E342">
         <v>164</v>
@@ -8421,6 +8421,52 @@
         <v>4</v>
       </c>
       <c r="G342">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A343" t="s">
+        <v>5</v>
+      </c>
+      <c r="B343" t="s">
+        <v>3</v>
+      </c>
+      <c r="C343">
+        <v>69</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>164</v>
+      </c>
+      <c r="F343">
+        <v>4</v>
+      </c>
+      <c r="G343">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A344" t="s">
+        <v>5</v>
+      </c>
+      <c r="B344" t="s">
+        <v>7</v>
+      </c>
+      <c r="C344">
+        <v>69</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>164</v>
+      </c>
+      <c r="F344">
+        <v>4</v>
+      </c>
+      <c r="G344">
         <v>4</v>
       </c>
     </row>
